--- a/Merton Model.xlsx
+++ b/Merton Model.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/luism/Desktop/8-ITESO/Módelos de Crédito/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E30FCABA-0A0C-8E49-8581-432515679349}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AE7ECD4-BCAB-E44B-B392-61B1A41CE33A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" xr2:uid="{32392DCD-070E-EC43-B159-7EFFE87224E1}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -127,13 +127,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -616,7 +619,7 @@
       <c r="B2" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="2">
+      <c r="C2" s="6">
         <v>100</v>
       </c>
     </row>
@@ -624,7 +627,7 @@
       <c r="B3" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="2">
+      <c r="C3" s="7">
         <v>60</v>
       </c>
     </row>
@@ -632,7 +635,7 @@
       <c r="B4" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="3">
+      <c r="C4" s="8">
         <v>0.03</v>
       </c>
     </row>
@@ -640,7 +643,7 @@
       <c r="B5" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="3">
+      <c r="C5" s="8">
         <v>0.2</v>
       </c>
     </row>

--- a/Merton Model.xlsx
+++ b/Merton Model.xlsx
@@ -1,19 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10215"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10302"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/luism/Desktop/8-ITESO/Módelos de Crédito/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AE7ECD4-BCAB-E44B-B392-61B1A41CE33A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E9207E6-2551-CB4B-9160-30B7F1A078F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" xr2:uid="{32392DCD-070E-EC43-B159-7EFFE87224E1}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
+    <sheet name="Hoja2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="34">
   <si>
     <t>Assets</t>
   </si>
@@ -69,12 +70,86 @@
   </si>
   <si>
     <t>objetivo</t>
+  </si>
+  <si>
+    <t>Working Capital</t>
+  </si>
+  <si>
+    <t>Current Assets</t>
+  </si>
+  <si>
+    <t>Non-Current Assets</t>
+  </si>
+  <si>
+    <t>Revenue</t>
+  </si>
+  <si>
+    <t>Retained earnings</t>
+  </si>
+  <si>
+    <t>Cost of Goods</t>
+  </si>
+  <si>
+    <t>Operating Expenses</t>
+  </si>
+  <si>
+    <t>Share price</t>
+  </si>
+  <si>
+    <t>Total Diluted Shares</t>
+  </si>
+  <si>
+    <t>Current liabilities</t>
+  </si>
+  <si>
+    <t>Non-Current Liabilities</t>
+  </si>
+  <si>
+    <t>x1</t>
+  </si>
+  <si>
+    <t>x2</t>
+  </si>
+  <si>
+    <t>x3</t>
+  </si>
+  <si>
+    <t>x4</t>
+  </si>
+  <si>
+    <t>x5</t>
+  </si>
+  <si>
+    <t>Total Assets</t>
+  </si>
+  <si>
+    <t>EBIT</t>
+  </si>
+  <si>
+    <t>MVE</t>
+  </si>
+  <si>
+    <t>Total Liabilities</t>
+  </si>
+  <si>
+    <t>Variables</t>
+  </si>
+  <si>
+    <t>Pesos</t>
+  </si>
+  <si>
+    <t>Altman</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="3">
+    <numFmt numFmtId="6" formatCode="&quot;$&quot;#,##0;[Red]\-&quot;$&quot;#,##0"/>
+    <numFmt numFmtId="44" formatCode="_-&quot;$&quot;* #,##0.00_-;\-&quot;$&quot;* #,##0.00_-;_-&quot;$&quot;* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+  </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
@@ -123,11 +198,13 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -137,8 +214,14 @@
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="6" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="3" applyFont="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="4">
+    <cellStyle name="Millares" xfId="2" builtinId="3"/>
+    <cellStyle name="Moneda" xfId="3" builtinId="4"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Porcentaje" xfId="1" builtinId="5"/>
   </cellStyles>
@@ -281,6 +364,55 @@
         <a:xfrm>
           <a:off x="9156550" y="2920999"/>
           <a:ext cx="4485203" cy="1282700"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>1</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>283308</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>165955</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Imagen 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{75042090-2A4D-3C9D-C3E4-6AFFB3F1DE48}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="1"/>
+          <a:ext cx="4435231" cy="3243262"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -759,7 +891,7 @@
         <v>1</v>
       </c>
       <c r="C24" s="2">
-        <v>110.54380047291831</v>
+        <v>110</v>
       </c>
       <c r="E24" t="s">
         <v>10</v>
@@ -795,7 +927,7 @@
       </c>
       <c r="C28" s="5">
         <f>(LN(C23/C24)+(C25+C26^2/2)*C27)/(C26*SQRT(C27))</f>
-        <v>-8.5432924317811472E-4</v>
+        <v>1.6581018314537461E-2</v>
       </c>
     </row>
     <row r="30" spans="2:5" x14ac:dyDescent="0.2">
@@ -804,8 +936,243 @@
       </c>
       <c r="C30" s="4">
         <f>1-_xlfn.NORM.S.DIST(C28,1)</f>
-        <v>0.50034082801502655</v>
-      </c>
+        <v>0.49338543383424072</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C6BCA24B-B22D-F74F-B26B-2A8DEDAE34B7}">
+  <dimension ref="G1:M29"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="7" max="7" width="27.6640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="7:13" x14ac:dyDescent="0.2">
+      <c r="J1" t="s">
+        <v>31</v>
+      </c>
+      <c r="M1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="2" spans="7:13" x14ac:dyDescent="0.2">
+      <c r="G2" t="s">
+        <v>11</v>
+      </c>
+      <c r="H2" s="10">
+        <v>500000</v>
+      </c>
+      <c r="J2" t="s">
+        <v>22</v>
+      </c>
+      <c r="K2">
+        <f>H2/H14</f>
+        <v>0.1</v>
+      </c>
+      <c r="M2">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="3" spans="7:13" x14ac:dyDescent="0.2">
+      <c r="G3" t="s">
+        <v>12</v>
+      </c>
+      <c r="H3" s="10">
+        <v>1200000</v>
+      </c>
+      <c r="J3" t="s">
+        <v>23</v>
+      </c>
+      <c r="K3">
+        <f>H5/H14</f>
+        <v>0.3</v>
+      </c>
+      <c r="M3">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="4" spans="7:13" x14ac:dyDescent="0.2">
+      <c r="G4" t="s">
+        <v>13</v>
+      </c>
+      <c r="H4" s="10">
+        <v>3800000</v>
+      </c>
+      <c r="J4" t="s">
+        <v>24</v>
+      </c>
+      <c r="K4">
+        <f>H15/H14</f>
+        <v>0.16</v>
+      </c>
+      <c r="M4">
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="5" spans="7:13" x14ac:dyDescent="0.2">
+      <c r="G5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H5" s="10">
+        <v>1500000</v>
+      </c>
+      <c r="J5" t="s">
+        <v>25</v>
+      </c>
+      <c r="K5" s="12">
+        <f>H16/H17</f>
+        <v>15.625</v>
+      </c>
+      <c r="M5">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="6" spans="7:13" x14ac:dyDescent="0.2">
+      <c r="G6" t="s">
+        <v>14</v>
+      </c>
+      <c r="H6" s="10">
+        <v>5000000</v>
+      </c>
+      <c r="J6" t="s">
+        <v>26</v>
+      </c>
+      <c r="K6">
+        <f>H6/H14</f>
+        <v>1</v>
+      </c>
+      <c r="M6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="7:13" x14ac:dyDescent="0.2">
+      <c r="G7" t="s">
+        <v>16</v>
+      </c>
+      <c r="H7" s="10">
+        <v>3000000</v>
+      </c>
+    </row>
+    <row r="8" spans="7:13" x14ac:dyDescent="0.2">
+      <c r="G8" t="s">
+        <v>17</v>
+      </c>
+      <c r="H8" s="10">
+        <v>1200000</v>
+      </c>
+      <c r="J8" t="s">
+        <v>33</v>
+      </c>
+      <c r="K8">
+        <f>SUMPRODUCT(K2:K6,M2:M6)</f>
+        <v>11.443</v>
+      </c>
+    </row>
+    <row r="9" spans="7:13" x14ac:dyDescent="0.2">
+      <c r="G9" t="s">
+        <v>18</v>
+      </c>
+      <c r="H9" s="10">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="10" spans="7:13" x14ac:dyDescent="0.2">
+      <c r="G10" t="s">
+        <v>19</v>
+      </c>
+      <c r="H10" s="10">
+        <v>1000000</v>
+      </c>
+    </row>
+    <row r="11" spans="7:13" x14ac:dyDescent="0.2">
+      <c r="G11" t="s">
+        <v>20</v>
+      </c>
+      <c r="H11" s="10">
+        <v>700000</v>
+      </c>
+    </row>
+    <row r="12" spans="7:13" x14ac:dyDescent="0.2">
+      <c r="G12" t="s">
+        <v>21</v>
+      </c>
+      <c r="H12" s="10">
+        <v>2500000</v>
+      </c>
+    </row>
+    <row r="14" spans="7:13" x14ac:dyDescent="0.2">
+      <c r="G14" t="s">
+        <v>27</v>
+      </c>
+      <c r="H14" s="11">
+        <f>H3+H4</f>
+        <v>5000000</v>
+      </c>
+    </row>
+    <row r="15" spans="7:13" x14ac:dyDescent="0.2">
+      <c r="G15" t="s">
+        <v>28</v>
+      </c>
+      <c r="H15" s="11">
+        <f>H6-H7-H8</f>
+        <v>800000</v>
+      </c>
+    </row>
+    <row r="16" spans="7:13" x14ac:dyDescent="0.2">
+      <c r="G16" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="H16" s="10">
+        <f>H9*H10</f>
+        <v>50000000</v>
+      </c>
+    </row>
+    <row r="17" spans="7:8" x14ac:dyDescent="0.2">
+      <c r="G17" t="s">
+        <v>30</v>
+      </c>
+      <c r="H17" s="11">
+        <f>H11+H12</f>
+        <v>3200000</v>
+      </c>
+    </row>
+    <row r="19" spans="7:8" x14ac:dyDescent="0.2">
+      <c r="H19" s="9"/>
+    </row>
+    <row r="20" spans="7:8" x14ac:dyDescent="0.2">
+      <c r="H20" s="9"/>
+    </row>
+    <row r="21" spans="7:8" x14ac:dyDescent="0.2">
+      <c r="H21" s="9"/>
+    </row>
+    <row r="22" spans="7:8" x14ac:dyDescent="0.2">
+      <c r="H22" s="9"/>
+    </row>
+    <row r="23" spans="7:8" x14ac:dyDescent="0.2">
+      <c r="H23" s="9"/>
+    </row>
+    <row r="24" spans="7:8" x14ac:dyDescent="0.2">
+      <c r="H24" s="9"/>
+    </row>
+    <row r="25" spans="7:8" x14ac:dyDescent="0.2">
+      <c r="H25" s="9"/>
+    </row>
+    <row r="27" spans="7:8" x14ac:dyDescent="0.2">
+      <c r="H27" s="9"/>
+    </row>
+    <row r="28" spans="7:8" x14ac:dyDescent="0.2">
+      <c r="H28" s="9"/>
+    </row>
+    <row r="29" spans="7:8" x14ac:dyDescent="0.2">
+      <c r="H29" s="9"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
